--- a/6.2 Geoffrey Bay/output/yearly_benthic_cover_growth_param_0.5.xlsx
+++ b/6.2 Geoffrey Bay/output/yearly_benthic_cover_growth_param_0.5.xlsx
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.30000290715221</v>
+        <v>87.85194562458794</v>
       </c>
       <c r="C3" t="n">
-        <v>46.04464539925263</v>
+        <v>45.8542530407194</v>
       </c>
       <c r="D3" t="n">
-        <v>2.229340468326959</v>
+        <v>2.228336502420531</v>
       </c>
       <c r="E3" t="n">
-        <v>5.787543668968896</v>
+        <v>5.654225682289177</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7431134894423197</v>
+        <v>0.7427788341401773</v>
       </c>
       <c r="G3" t="n">
-        <v>34.01049876422792</v>
+        <v>33.9491197485929</v>
       </c>
       <c r="H3" t="n">
-        <v>34.1832205143467</v>
+        <v>34.16782637044815</v>
       </c>
       <c r="I3" t="n">
-        <v>6.701826692824918</v>
+        <v>6.467290773320896</v>
       </c>
       <c r="J3" t="n">
-        <v>4.644459309014498</v>
+        <v>4.642367713376108</v>
       </c>
       <c r="K3" t="n">
-        <v>11.69999709284778</v>
+        <v>12.14805437541206</v>
       </c>
       <c r="L3" t="n">
-        <v>49.01486210441896</v>
+        <v>48.76550895213084</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7595045965194</v>
+        <v>106.7678163682623</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.93732486278169</v>
+        <v>87.04454933616526</v>
       </c>
       <c r="C4" t="n">
-        <v>43.33862760948792</v>
+        <v>42.665299308648</v>
       </c>
       <c r="D4" t="n">
-        <v>2.214790904689216</v>
+        <v>2.189846737042707</v>
       </c>
       <c r="E4" t="n">
-        <v>6.68255580532415</v>
+        <v>6.456653466798741</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7446899857430531</v>
+        <v>0.7443149892530707</v>
       </c>
       <c r="G4" t="n">
-        <v>33.78853270603633</v>
+        <v>33.36272103704839</v>
       </c>
       <c r="H4" t="n">
-        <v>34.25573934418044</v>
+        <v>34.23848950564124</v>
       </c>
       <c r="I4" t="n">
-        <v>5.59670370591443</v>
+        <v>5.400554917549414</v>
       </c>
       <c r="J4" t="n">
-        <v>4.654312410894082</v>
+        <v>4.651968682831692</v>
       </c>
       <c r="K4" t="n">
-        <v>12.0626751372183</v>
+        <v>12.95545066383475</v>
       </c>
       <c r="L4" t="n">
-        <v>44.4125354007153</v>
+        <v>44.19960306159167</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81383814742152</v>
+        <v>99.82035303407442</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>87.42042487901873</v>
+        <v>86.11715188695929</v>
       </c>
       <c r="C5" t="n">
-        <v>43.69098937718454</v>
+        <v>42.57621585281884</v>
       </c>
       <c r="D5" t="n">
-        <v>2.191869043979308</v>
+        <v>2.145240574954232</v>
       </c>
       <c r="E5" t="n">
-        <v>7.392099817024435</v>
+        <v>7.076520411607755</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7460166634460297</v>
+        <v>0.7456138428164314</v>
       </c>
       <c r="G5" t="n">
-        <v>33.43884008329702</v>
+        <v>32.68313788763544</v>
       </c>
       <c r="H5" t="n">
-        <v>34.31676651851736</v>
+        <v>34.29823676955584</v>
       </c>
       <c r="I5" t="n">
-        <v>4.672228606216872</v>
+        <v>4.508315882786921</v>
       </c>
       <c r="J5" t="n">
-        <v>4.662604146537686</v>
+        <v>4.660086517602696</v>
       </c>
       <c r="K5" t="n">
-        <v>12.57957512098129</v>
+        <v>13.88284811304069</v>
       </c>
       <c r="L5" t="n">
-        <v>43.57397151000322</v>
+        <v>43.39092061976411</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84453600816904</v>
+        <v>99.84998458562364</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>86.68189535102201</v>
+        <v>84.95967120672125</v>
       </c>
       <c r="C6" t="n">
-        <v>43.67921671950243</v>
+        <v>42.1191870204962</v>
       </c>
       <c r="D6" t="n">
-        <v>2.157473689519781</v>
+        <v>2.08906487370303</v>
       </c>
       <c r="E6" t="n">
-        <v>7.925994837789041</v>
+        <v>7.518292526403532</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7471353088578363</v>
+        <v>0.746714503874499</v>
       </c>
       <c r="G6" t="n">
-        <v>32.91410948383913</v>
+        <v>31.82729066408251</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36822420746046</v>
+        <v>34.34886717822695</v>
       </c>
       <c r="I6" t="n">
-        <v>3.899362143194272</v>
+        <v>3.762475811215108</v>
       </c>
       <c r="J6" t="n">
-        <v>4.669595680361477</v>
+        <v>4.666965649215619</v>
       </c>
       <c r="K6" t="n">
-        <v>13.318104648978</v>
+        <v>15.04032879327875</v>
       </c>
       <c r="L6" t="n">
-        <v>42.87289450356911</v>
+        <v>42.71525318948096</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87021587204953</v>
+        <v>99.87476900325591</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85.81798682371593</v>
+        <v>83.70898782078038</v>
       </c>
       <c r="C7" t="n">
-        <v>43.42238286814337</v>
+        <v>41.45324526701368</v>
       </c>
       <c r="D7" t="n">
-        <v>2.116797395204393</v>
+        <v>2.028540226926995</v>
       </c>
       <c r="E7" t="n">
-        <v>8.3188232513205</v>
+        <v>7.823690962449541</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7480795012621737</v>
+        <v>0.7476479650957321</v>
       </c>
       <c r="G7" t="n">
-        <v>32.29355776587518</v>
+        <v>30.90518644916303</v>
       </c>
       <c r="H7" t="n">
-        <v>34.41165705805999</v>
+        <v>34.39180639440367</v>
       </c>
       <c r="I7" t="n">
-        <v>3.253574969105117</v>
+        <v>3.139316040893092</v>
       </c>
       <c r="J7" t="n">
-        <v>4.675496882888585</v>
+        <v>4.672799781848326</v>
       </c>
       <c r="K7" t="n">
-        <v>14.18201317628406</v>
+        <v>16.29101217921963</v>
       </c>
       <c r="L7" t="n">
-        <v>42.28728834048383</v>
+        <v>42.15122933678849</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89168438491127</v>
+        <v>99.89548678302179</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>90.59027223153673</v>
+        <v>89.19082892120699</v>
       </c>
       <c r="C8" t="n">
-        <v>45.75536429371601</v>
+        <v>43.99547182026617</v>
       </c>
       <c r="D8" t="n">
-        <v>2.121138737094547</v>
+        <v>2.033048180651944</v>
       </c>
       <c r="E8" t="n">
-        <v>10.16738950089369</v>
+        <v>9.835380394894589</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7496137382578129</v>
+        <v>0.7493094369189012</v>
       </c>
       <c r="G8" t="n">
-        <v>32.81106203975873</v>
+        <v>31.47550340016102</v>
       </c>
       <c r="H8" t="n">
-        <v>34.48223195985938</v>
+        <v>34.46823409826944</v>
       </c>
       <c r="I8" t="n">
-        <v>5.573750391561233</v>
+        <v>5.946169429567954</v>
       </c>
       <c r="J8" t="n">
-        <v>4.68508586411133</v>
+        <v>4.683183980743133</v>
       </c>
       <c r="K8" t="n">
-        <v>9.409727768463275</v>
+        <v>10.80917107879301</v>
       </c>
       <c r="L8" t="n">
-        <v>44.64949651856677</v>
+        <v>44.9975909420799</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81458858074605</v>
+        <v>99.80223384113907</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>93.02513416527037</v>
+        <v>91.99830229025562</v>
       </c>
       <c r="C9" t="n">
-        <v>47.64154398803832</v>
+        <v>46.06818777739797</v>
       </c>
       <c r="D9" t="n">
-        <v>2.125720939676272</v>
+        <v>2.037891976584055</v>
       </c>
       <c r="E9" t="n">
-        <v>11.72175842093228</v>
+        <v>11.54389564139134</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7512330957975493</v>
+        <v>0.7510946882656134</v>
       </c>
       <c r="G9" t="n">
-        <v>33.14574946059257</v>
+        <v>31.84506425733797</v>
       </c>
       <c r="H9" t="n">
-        <v>34.55672240668726</v>
+        <v>34.5503556602182</v>
       </c>
       <c r="I9" t="n">
-        <v>6.028742992849763</v>
+        <v>6.575658264798355</v>
       </c>
       <c r="J9" t="n">
-        <v>4.695206848734683</v>
+        <v>4.694341801660084</v>
       </c>
       <c r="K9" t="n">
-        <v>6.974865834729634</v>
+        <v>8.001697709744382</v>
       </c>
       <c r="L9" t="n">
-        <v>45.18306526261071</v>
+        <v>45.7114468859594</v>
       </c>
       <c r="M9" t="n">
-        <v>99.79947508537867</v>
+        <v>99.78133237310175</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>91.66863372735847</v>
+        <v>90.35907864840262</v>
       </c>
       <c r="C10" t="n">
-        <v>47.22528689476034</v>
+        <v>45.45200879183687</v>
       </c>
       <c r="D10" t="n">
-        <v>2.068138339130525</v>
+        <v>1.96833374386196</v>
       </c>
       <c r="E10" t="n">
-        <v>12.24309140442231</v>
+        <v>12.06501005538039</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7526079996890006</v>
+        <v>0.7526160708059555</v>
       </c>
       <c r="G10" t="n">
-        <v>32.2478806880013</v>
+        <v>30.75811440125435</v>
       </c>
       <c r="H10" t="n">
-        <v>34.61996798569402</v>
+        <v>34.62033925707394</v>
       </c>
       <c r="I10" t="n">
-        <v>5.033147312365055</v>
+        <v>5.4908146774888</v>
       </c>
       <c r="J10" t="n">
-        <v>4.703799998056254</v>
+        <v>4.703850442537222</v>
       </c>
       <c r="K10" t="n">
-        <v>8.331366272641537</v>
+        <v>9.640921351597367</v>
       </c>
       <c r="L10" t="n">
-        <v>44.27588174946341</v>
+        <v>44.72441268254359</v>
       </c>
       <c r="M10" t="n">
-        <v>99.83253491686528</v>
+        <v>99.81734282597783</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>90.16011947492099</v>
+        <v>88.57319570170822</v>
       </c>
       <c r="C11" t="n">
-        <v>46.50225241663414</v>
+        <v>44.52080447425946</v>
       </c>
       <c r="D11" t="n">
-        <v>2.004238634232619</v>
+        <v>1.893114123464987</v>
       </c>
       <c r="E11" t="n">
-        <v>12.56494795901997</v>
+        <v>12.36787588191216</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7537768676854943</v>
+        <v>0.7539143077279242</v>
       </c>
       <c r="G11" t="n">
-        <v>31.25151114126561</v>
+        <v>29.58269702267017</v>
       </c>
       <c r="H11" t="n">
-        <v>34.67373591353273</v>
+        <v>34.6800581554845</v>
       </c>
       <c r="I11" t="n">
-        <v>4.200803536150219</v>
+        <v>4.583571787148956</v>
       </c>
       <c r="J11" t="n">
-        <v>4.71110542303434</v>
+        <v>4.711964423299527</v>
       </c>
       <c r="K11" t="n">
-        <v>9.839880525079016</v>
+        <v>11.42680429829178</v>
       </c>
       <c r="L11" t="n">
-        <v>43.51805741072116</v>
+        <v>43.89986859751849</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8601903524343</v>
+        <v>99.84747737006974</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>88.54577281996571</v>
+        <v>86.66074079620012</v>
       </c>
       <c r="C12" t="n">
-        <v>45.54357288282483</v>
+        <v>43.32175362292674</v>
       </c>
       <c r="D12" t="n">
-        <v>1.936177223915715</v>
+        <v>1.81320071925323</v>
       </c>
       <c r="E12" t="n">
-        <v>12.72247304668958</v>
+        <v>12.48333867100253</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7547715343199176</v>
+        <v>0.7550235838307552</v>
       </c>
       <c r="G12" t="n">
-        <v>30.19024933018224</v>
+        <v>28.33393235732625</v>
       </c>
       <c r="H12" t="n">
-        <v>34.7194905787162</v>
+        <v>34.73108485621471</v>
       </c>
       <c r="I12" t="n">
-        <v>3.505289016642561</v>
+        <v>3.825263209630426</v>
       </c>
       <c r="J12" t="n">
-        <v>4.717322089499485</v>
+        <v>4.71889739894222</v>
       </c>
       <c r="K12" t="n">
-        <v>11.4542271800343</v>
+        <v>13.33925920379987</v>
       </c>
       <c r="L12" t="n">
-        <v>42.88551095002558</v>
+        <v>43.21166573474149</v>
       </c>
       <c r="M12" t="n">
-        <v>99.88331101288472</v>
+        <v>99.87267856146809</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>86.77818516585451</v>
+        <v>84.57694122923499</v>
       </c>
       <c r="C13" t="n">
-        <v>44.32292917775219</v>
+        <v>41.83298232134071</v>
       </c>
       <c r="D13" t="n">
-        <v>1.861957687979338</v>
+        <v>1.726739898489798</v>
       </c>
       <c r="E13" t="n">
-        <v>12.72217470363103</v>
+        <v>12.42003693688373</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7556193742235132</v>
+        <v>0.7559733426384777</v>
       </c>
       <c r="G13" t="n">
-        <v>29.03296565417761</v>
+        <v>26.98285466302723</v>
       </c>
       <c r="H13" t="n">
-        <v>34.75849121428159</v>
+        <v>34.77477376136995</v>
       </c>
       <c r="I13" t="n">
-        <v>2.92435544266448</v>
+        <v>3.1917292353353</v>
       </c>
       <c r="J13" t="n">
-        <v>4.722621088896958</v>
+        <v>4.724833391490486</v>
       </c>
       <c r="K13" t="n">
-        <v>13.22181483414547</v>
+        <v>15.42305877076504</v>
       </c>
       <c r="L13" t="n">
-        <v>42.35788684875115</v>
+        <v>42.63770159651562</v>
       </c>
       <c r="M13" t="n">
-        <v>99.90263086064883</v>
+        <v>99.89374268862136</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>90.77535130874132</v>
+        <v>89.15248308371318</v>
       </c>
       <c r="C14" t="n">
-        <v>46.8499548563305</v>
+        <v>44.73910966873378</v>
       </c>
       <c r="D14" t="n">
-        <v>1.86426769696896</v>
+        <v>1.72911290385564</v>
       </c>
       <c r="E14" t="n">
-        <v>14.25966125095622</v>
+        <v>14.17211733310967</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7565568217060514</v>
+        <v>0.7570122534785431</v>
       </c>
       <c r="G14" t="n">
-        <v>30.02759275813401</v>
+        <v>28.14235075633184</v>
       </c>
       <c r="H14" t="n">
-        <v>35.76022160291493</v>
+        <v>35.94497804868035</v>
       </c>
       <c r="I14" t="n">
-        <v>3.378571042398339</v>
+        <v>3.675585204016239</v>
       </c>
       <c r="J14" t="n">
-        <v>4.728480135662822</v>
+        <v>4.731326584240894</v>
       </c>
       <c r="K14" t="n">
-        <v>9.224648691258668</v>
+        <v>10.84751691628681</v>
       </c>
       <c r="L14" t="n">
-        <v>43.81291696360125</v>
+        <v>44.29102205188216</v>
       </c>
       <c r="M14" t="n">
-        <v>99.88752051119042</v>
+        <v>99.87764863690276</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>89.90227325787758</v>
+        <v>88.24516167292532</v>
       </c>
       <c r="C15" t="n">
-        <v>46.50424645501239</v>
+        <v>44.40376978099009</v>
       </c>
       <c r="D15" t="n">
-        <v>1.830911437411475</v>
+        <v>1.695453888796801</v>
       </c>
       <c r="E15" t="n">
-        <v>14.47425774795771</v>
+        <v>14.40733132559265</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7573474184668894</v>
+        <v>0.7578891306611723</v>
       </c>
       <c r="G15" t="n">
-        <v>29.49032647413668</v>
+        <v>27.59453007568903</v>
       </c>
       <c r="H15" t="n">
-        <v>35.79759079258446</v>
+        <v>35.98661453598444</v>
       </c>
       <c r="I15" t="n">
-        <v>2.818418021902318</v>
+        <v>3.066535649568907</v>
       </c>
       <c r="J15" t="n">
-        <v>4.733421365418058</v>
+        <v>4.736807066632327</v>
       </c>
       <c r="K15" t="n">
-        <v>10.0977267421224</v>
+        <v>11.75483832707468</v>
       </c>
       <c r="L15" t="n">
-        <v>43.30417760724303</v>
+        <v>43.73929230293479</v>
       </c>
       <c r="M15" t="n">
-        <v>99.90615080437783</v>
+        <v>99.89790041099955</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>88.11540407885504</v>
+        <v>86.25044668743665</v>
       </c>
       <c r="C16" t="n">
-        <v>45.15742084643661</v>
+        <v>42.88639716435778</v>
       </c>
       <c r="D16" t="n">
-        <v>1.761036772426886</v>
+        <v>1.619658622331654</v>
       </c>
       <c r="E16" t="n">
-        <v>14.31365911785938</v>
+        <v>14.189580349961</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7580209101781789</v>
+        <v>0.7586383672312079</v>
       </c>
       <c r="G16" t="n">
-        <v>28.36486150594589</v>
+        <v>26.36091660269057</v>
       </c>
       <c r="H16" t="n">
-        <v>35.82942477008945</v>
+        <v>36.02219030366779</v>
       </c>
       <c r="I16" t="n">
-        <v>2.350770313741619</v>
+        <v>2.557972646359385</v>
       </c>
       <c r="J16" t="n">
-        <v>4.737630688613618</v>
+        <v>4.74148979519505</v>
       </c>
       <c r="K16" t="n">
-        <v>11.88459592114497</v>
+        <v>13.74955331256334</v>
       </c>
       <c r="L16" t="n">
-        <v>42.87969384292111</v>
+        <v>43.27886797725753</v>
       </c>
       <c r="M16" t="n">
-        <v>99.9217106105027</v>
+        <v>99.91481845417866</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>89.05327747819908</v>
+        <v>87.30782823481866</v>
       </c>
       <c r="C17" t="n">
-        <v>45.96662014116227</v>
+        <v>43.78869496750457</v>
       </c>
       <c r="D17" t="n">
-        <v>1.762519473166339</v>
+        <v>1.621173746956424</v>
       </c>
       <c r="E17" t="n">
-        <v>14.89800062321815</v>
+        <v>14.8373891245766</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7586591240880977</v>
+        <v>0.7593480425020575</v>
       </c>
       <c r="G17" t="n">
-        <v>28.58614240764359</v>
+        <v>26.61174659280774</v>
       </c>
       <c r="H17" t="n">
-        <v>36.05699044314725</v>
+        <v>36.28205802154386</v>
       </c>
       <c r="I17" t="n">
-        <v>2.249345881385033</v>
+        <v>2.450187440794115</v>
       </c>
       <c r="J17" t="n">
-        <v>4.741619525550611</v>
+        <v>4.745925265637859</v>
       </c>
       <c r="K17" t="n">
-        <v>10.94672252180096</v>
+        <v>12.69217176518136</v>
       </c>
       <c r="L17" t="n">
-        <v>43.01174221559966</v>
+        <v>43.43753668289981</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92508487856287</v>
+        <v>99.91840341558573</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>87.29294493962226</v>
+        <v>85.36231844426682</v>
       </c>
       <c r="C18" t="n">
-        <v>44.55739823973175</v>
+        <v>42.22445152751241</v>
       </c>
       <c r="D18" t="n">
-        <v>1.695161568239424</v>
+        <v>1.549179614808727</v>
       </c>
       <c r="E18" t="n">
-        <v>14.64127920826977</v>
+        <v>14.51905611066053</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7592025398715131</v>
+        <v>0.7599539661361436</v>
       </c>
       <c r="G18" t="n">
-        <v>27.49367069777807</v>
+        <v>25.42995494062951</v>
       </c>
       <c r="H18" t="n">
-        <v>36.08281750709092</v>
+        <v>36.31100937878461</v>
       </c>
       <c r="I18" t="n">
-        <v>1.875797544175606</v>
+        <v>2.0434521448964</v>
       </c>
       <c r="J18" t="n">
-        <v>4.745015874196958</v>
+        <v>4.749712288350898</v>
       </c>
       <c r="K18" t="n">
-        <v>12.70705506037774</v>
+        <v>14.63768155573318</v>
       </c>
       <c r="L18" t="n">
-        <v>42.67306486985206</v>
+        <v>43.06980615451015</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93751816996155</v>
+        <v>99.93193923775574</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>86.44285941999196</v>
+        <v>84.43088530986266</v>
       </c>
       <c r="C19" t="n">
-        <v>43.99975593121956</v>
+        <v>41.61052429573303</v>
       </c>
       <c r="D19" t="n">
-        <v>1.663286475433752</v>
+        <v>1.515426860876417</v>
       </c>
       <c r="E19" t="n">
-        <v>14.62665542923837</v>
+        <v>14.4867258793532</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7596604432526926</v>
+        <v>0.7604652239824489</v>
       </c>
       <c r="G19" t="n">
-        <v>26.9766914779327</v>
+        <v>24.87589974688957</v>
       </c>
       <c r="H19" t="n">
-        <v>36.10458040074743</v>
+        <v>36.33543755375231</v>
       </c>
       <c r="I19" t="n">
-        <v>1.564107423057702</v>
+        <v>1.704022395118411</v>
       </c>
       <c r="J19" t="n">
-        <v>4.74787777032933</v>
+        <v>4.752907649890306</v>
       </c>
       <c r="K19" t="n">
-        <v>13.55714058000801</v>
+        <v>15.56911469013734</v>
       </c>
       <c r="L19" t="n">
-        <v>42.39099800143421</v>
+        <v>42.76359845454918</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94789451266179</v>
+        <v>99.94323744041954</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>84.59629016307416</v>
+        <v>82.33042627914956</v>
       </c>
       <c r="C20" t="n">
-        <v>42.39696171103103</v>
+        <v>39.77472845748832</v>
       </c>
       <c r="D20" t="n">
-        <v>1.593117558096123</v>
+        <v>1.438385831020693</v>
       </c>
       <c r="E20" t="n">
-        <v>14.22695079796621</v>
+        <v>13.98705793509254</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7600507943238445</v>
+        <v>0.7609026872084149</v>
       </c>
       <c r="G20" t="n">
-        <v>25.83862821443858</v>
+        <v>23.61126270991652</v>
       </c>
       <c r="H20" t="n">
-        <v>36.12313271811252</v>
+        <v>36.35633978205659</v>
       </c>
       <c r="I20" t="n">
-        <v>1.304092615612853</v>
+        <v>1.420835538802191</v>
       </c>
       <c r="J20" t="n">
-        <v>4.75031746452403</v>
+        <v>4.755641795052593</v>
       </c>
       <c r="K20" t="n">
-        <v>15.40370983692584</v>
+        <v>17.66957372085043</v>
       </c>
       <c r="L20" t="n">
-        <v>42.15588102362484</v>
+        <v>42.50836386624129</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95655257158172</v>
+        <v>99.95266604458006</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>88.66551658745267</v>
+        <v>86.76108312084654</v>
       </c>
       <c r="C21" t="n">
-        <v>44.6239141284146</v>
+        <v>42.23884498426602</v>
       </c>
       <c r="D21" t="n">
-        <v>1.594420854035766</v>
+        <v>1.439660691833994</v>
       </c>
       <c r="E21" t="n">
-        <v>15.52341343083719</v>
+        <v>15.41339841745828</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7606725758798446</v>
+        <v>0.7615770855497621</v>
       </c>
       <c r="G21" t="n">
-        <v>26.78191315249055</v>
+        <v>24.66164564892874</v>
       </c>
       <c r="H21" t="n">
-        <v>37.07483119281327</v>
+        <v>37.41801885522932</v>
       </c>
       <c r="I21" t="n">
-        <v>2.176061782147039</v>
+        <v>2.306925637160437</v>
       </c>
       <c r="J21" t="n">
-        <v>4.75420359924903</v>
+        <v>4.759856784686013</v>
       </c>
       <c r="K21" t="n">
-        <v>11.33448341254732</v>
+        <v>13.23891687915345</v>
       </c>
       <c r="L21" t="n">
-        <v>43.96912635747292</v>
+        <v>44.44540871030131</v>
       </c>
       <c r="M21" t="n">
-        <v>99.92752389843484</v>
+        <v>99.92317057372078</v>
       </c>
     </row>
   </sheetData>
